--- a/DATA_ISSUES.xlsx
+++ b/DATA_ISSUES.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'register'!$A$1:$K$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'register'!$A$1:$K$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>data/outputs/precision_sample.csv; 01_Pipeline/scripts/precision_labels.py</t>
+          <t>data/outputs/precision_sample.csv; 01_Pipeline/scripts/precision_labels.py.  Checked 10 September 2026: the script this entry names, 01_Pipeline/scripts/precision_labels.py, was deleted in the 27 August cleanup. The current equivalents are pv2.calcs.labels, which applies the reviewers' marks, and pv2.dashboard.handcode, which scores a blind hand-coding pack. Whether precision is now measured was NOT re-verified today; the entry stays open on its original claim.</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>01_Pipeline/scripts/precision_recall.py L28-33</t>
+          <t>01_Pipeline/scripts/precision_recall.py L28-33.  Checked 10 September 2026: 01_Pipeline/scripts/precision_recall.py was deleted in the 27 August cleanup; the recall bound now lives in pv2.validate.recall. The claim itself was not re-verified today.</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>STALE</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>pv2-sources: Cambodia/ 6 objects, all under NDPs/. Indonesia/Budget/ holds only .emptyFolderPlaceholder.</t>
+          <t>pv2-sources: Cambodia/ 6 objects, all under NDPs/. Indonesia/Budget/ holds only .emptyFolderPlaceholder. UPDATE 2026-09-19: no longer true. data/calcs/shares.csv holds Cambodia FY2022, 2023 and 2026 and Indonesia FY2020 and 2021, so both countries now have budget layers; Cambodia's carries its own fault, recorded in W107.</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>brunei, malaysia</t>
+          <t>all with a sector layer</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Prompt 7 returns SDG goal names in the HDICategory field on 38 sector interventions</t>
+          <t>Prompt 7 returns SDG goal names in the HDICategory field: 2,257 of 24,605 published sector responses on 12 September 2026</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The L2 gate now has a sector-responses contract and catches this; before 2026-08-24 no schema contract existed for any sector stage, so the field was never checked. Correcting the data needs a re-run of stage 7 for both countries, which costs money and is therefore on the human list. Tightening Prompt 7 to name the fifteen values inline, as Prompt 3 does, should come first.</t>
+          <t>The L2 gate now has a sector-responses contract and catches this; before 2026-08-24 no schema contract existed for any sector stage, so the field was never checked. Correcting the data needs a re-run of stage 7 for both countries, which costs money and is therefore on the human list. Tightening Prompt 7 to name the fifteen values inline, as Prompt 3 does, should come first.  From 13 September 2026 publish.sector.hdi_of publishes a value outside the fifteen as null and the run report counts what it nulled, validate.sector notes each one and check_publishable fails if a non-null value outside the fifteen ever reaches the payload, and validate.truth's vocab check lists every workbook row. What is published is now inside the vocabulary; the workbook rows are not, and stay so until stage 7 is re-run under a prompt that names the fifteen inline.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>validate_stage_schema.py on brunei_sector_responses.xlsx: 4 blocking; malaysia_sector_responses.xlsx: 34 blocking. All HDICategory, all 'value outside the fixed vocabulary'.</t>
+          <t>validate_stage_schema.py on brunei_sector_responses.xlsx: 4 blocking; malaysia_sector_responses.xlsx: 34 blocking. All HDICategory, all 'value outside the fixed vocabulary'.  Checked 10 September 2026: VERIFIED STILL TRUE. validate_stage_schema.py was deleted in the 27 August cleanup and its work is now pv2.extract.schemas. normalise_stage3 clamps HDICategory against vocab.HDI, which is what closed W83; the stage 7 normaliser does not clamp it at all, so a sector intervention can still carry an SDG goal name in that field.  Measured 12 September 2026 on the published sector layer: 2,257 of 24,605 responses (9.2%) carry a value outside the fifteen, 'Education' 289, 'Governance' 235, 'Industry, Innovation and Infrastructure' 228, 'Health' 209, 'Quality Education' 78; india 295, cambodia 261, pakistan 260. On disk, all 29 countries: 2,737. The publisher passed the value through and the page grouped by it.</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>141 marked, 140 excluded, 'OVERALL 1 labelled y/n, precision 100%'. Rejoined to the 2026-08-16 runs: 114 joined, 97 y, 7 n, 10 unsure.</t>
+          <t>141 marked, 140 excluded, 'OVERALL 1 labelled y/n, precision 100%'. Rejoined to the 2026-08-16 runs: 114 joined, 97 y, 7 n, 10 unsure.  Checked 10 September 2026: precision_labels.py no longer exists, so the specific script that reported 100% from one edge is gone. Whether pv2.calcs.labels can discard silently in the same way was NOT checked today.</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>countable programmes / national line: brunei 41.5%, fiji 58.0%, maldives 112.6%, brazil 100.0%, jamaica 100%, kenya 100.3%, malaysia 100%, thailand 100%. Corrected from an earlier reading of this issue that summed 'national' and 'grand_total' together and so halved every coverage figure.</t>
+          <t>countable programmes / national line: brunei 41.5%, fiji 58.0%, maldives 112.6%, brazil 100.0%, jamaica 100%, kenya 100.3%, malaysia 100%, thailand 100%. Corrected from an earlier reading of this issue that summed 'national' and 'grand_total' together and so halved every coverage figure.  Checked 10 September 2026: coverage_basis.py was deleted in the 27 August cleanup. The basis now travels with the figures: every share in calcs carries denominator_basis and coverage, and comparability.csv says per country-year whether a share may be set beside another's. W122 removed the 40% threshold from that rule on 10 September.</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>bhutan_budget_2024/25/26/27.xlsx and kiribati_budget_2023/24/25/26.xlsx: 0 data rows each, header only. Dry run: 'reusing 4 budget file(s)', Estimated total $0.0000. mappings/ empty for both.</t>
+          <t>bhutan_budget_2024/25/26/27.xlsx and kiribati_budget_2023/24/25/26.xlsx: 0 data rows each, header only. Dry run: 'reusing 4 budget file(s)', Estimated total $0.0000. mappings/ empty for both.  Checked 10 September 2026: the bhutan and kiribati workbooks this entry names are no longer on the live path: those years were rejected and their mappings retired with them under W124.</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Include every held document and let the extraction produce the evidence. config_completeness.py is registered as an L2 gate: a document we hold is either in the run, or the config carries a reason naming a date, a cost or a row count. Predictions no longer pass. Brazil is exempt because its budget layer is pre-built and its one exclusion cites 439 pages, 10,214 chunks and $38, which is a measurement.</t>
+          <t>PROPOSED, NOT BUILT. Register a config-completeness gate so that a document held on disk is either in the country's run or the config carries a reason naming a date, a cost or a row count, and fail the suite on an exclusion without one. The file this entry used to name as landed, config_completeness.py, does not exist and never did: the suite's L2 checks the opposite direction, that every document a config NAMES is present, and nothing anywhere checks a document that is held and left out. The register README stated the rule as though a suite enforced it, which was corrected on 10 September.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>held vs configured budget documents: kiribati 14/4, malaysia 10/5, fiji 11/8, ghana 4/2, bhutan 5/4, kenya 3/2. Bhutan and Kiribati were each called blocked for eleven days and produced 390 and 300 rows on a re-run costing $1.04 and $1.43.</t>
+          <t>held vs configured budget documents: kiribati 14/4, malaysia 10/5, fiji 11/8, ghana 4/2, bhutan 5/4, kenya 3/2. Bhutan and Kiribati were each called blocked for eleven days and produced 390 and 300 rows on a re-run costing $1.04 and $1.43.  Checked 10 September 2026: grep for config_completeness and document_shape across the package and support returns nothing but this register; pv2.validate.suite L2 reads 'every configured document exists', which is the other direction.</t>
         </is>
       </c>
     </row>
@@ -4234,17 +4234,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Rate limiting is handled blind: the client never reads Retry-After</t>
+          <t>A rate-limited call still counts as an error, so a burst of 429s can abort a stage and stop the country</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>llm.py backs off on a generic 2**attempt and treats a 429 the same as a DNS blip, so the wait bears no relation to what the API asked for. After MAX_RETRIES the call is an error, and past FAILURE_RATE_ABORT (20%) the whole stage aborts and the country stops. That makes concurrency a gamble rather than a setting: 12 ran 13,850 calls with 0 errors on 26 August, but nobody can say where the ceiling is, so going higher risks losing a country mid-stage rather than merely running slower.</t>
+          <t>Half of this is now done and the entry's original headline, that the client never reads Retry-After, is no longer true: llm.retry_after reads the header and the error body and the call sleeps for what the service asks, falling back to an exponential backoff only where it says nothing. What is not done is the second half. A 429 still arrives at the generic `except Exception`, which calls ledger.record_error, so it counts towards FAILURE_RATE_ABORT (20%, and zero for stages 5 and 5c). A service that asks us to slow down can therefore end a country mid-stage, which is the same outcome the backoff was written to avoid. That keeps concurrency a gamble rather than a setting: 12 workers ran 13,850 calls with no errors on 26 August, but nobody can say where the ceiling is.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Read Retry-After (and the reset headers) and sleep for what the API asks. Count a 429 as a pause rather than an error so it never reaches FAILURE_RATE_ABORT. Then concurrency can be raised until throughput plateaus instead of until it breaks.</t>
+          <t>Separate a rate-limit response from a failure: catch it before the generic handler, sleep on what retry_after returns and retry without calling record_error, so it never reaches FAILURE_RATE_ABORT. Then concurrency can be raised until throughput plateaus rather than until a country breaks.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>02_Automation/llm.py:388 sleeps (4**attempt if transient else 2**attempt)+0.5 with no reference to the response headers; llm.py:441 aborts the stage above a 20% error rate. Bangladesh at concurrency 4 ran 26 chunks/min and at 12 ran 113 chunks/min with 0 errors across 13,850 calls.</t>
+          <t>llm.py: retry_after is defined and read on every retry; the 429 path still goes through `except Exception` to ledger.record_error, checked 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>support/platform/note_claims.py computes every count the note states and rewrites the Appendix A inventory between markers; support/platform/check_note.py holds the prose to those counts and to the house rules (no em dash, % never percent, British spelling, no AI tells, no numeral opening a sentence) and reads the built .docx so it tests what circulates; support/platform/test_check_note.py proves the gate fires; pv2.validate.suite runs it. The note is on the publish manifest and the landing page.</t>
+          <t>support/platform/note_claims.py computes every count the note states and rewrites the Appendix A inventory between markers; support/platform/check_note.py holds the prose to those counts and to the house rules (no em dash, % never percent, British spelling, no AI tells, no numeral opening a sentence) and reads the built .docx so it tests what circulates; support/platform/test_check_note.py proves the gate fires and pv2.validate.suite runs the gate at L7. It did not run the PROOF, and nor did anything else, until that file was rewritten as pytest on 10 September so the support suite collects it (W131). The note is on the publish manifest and the landing page.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>The rule was every extracted year comparable, which one country met (Rwanda, three years) and Thailand, comparable on four of five years with the fifth a between-plans year at 138%, did not. Sebastian set the base on 1 September: a country whose latest two plans are held and whose budgets cover 40% of those plans' years is enough to do the analysis off (a 2020-2025 plan with the 2020 and 2024 budgets was his example). Years outside the two plans do not count towards the share, and a document spanning ten years or more is a vision, not a plan, under the coverage grid's rule (W96).</t>
+          <t>The rule was every extracted year comparable, which one country met (Rwanda, three years) and Thailand, comparable on four of five years with the fifth a between-plans year at 138%, did not. The base was set on 1 September: a country whose latest two plans are held and whose budgets cover 40% of those plans' years is enough to do the analysis off (a 2020-2025 plan with the 2020 and 2024 budgets is the worked example). Years outside the two plans do not count towards the share, and a document spanning ten years or more is a vision, not a plan, under the coverage grid's rule (W96).</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>calcs.comparability takes the union documents and applies the rule (plan_slots, BASE_PLANS=2, BASE_YEARS_SHARE=0.40, VISION_SPAN=10). comparability.csv now carries plans, plan_years, held_in_plans, extracted_in_plans, comparable_in_plans and share_of_plan_years, so the base set can be read at all three grades; why_not states the rule reason and years_why_not the per-year ones. The per-year rule (printed denominator, coverage 0.90 to 1.05) is unchanged underneath. Outcome on 1 September: Thailand is the one comparable country (2017-2021 and 2023-2027, FY2023 to FY2026, 4 of 10 years); Rwanda drops (2017-2024 and 2024-2029 span 13 years, three comparable, 23%). Inclusive counting: his 2020-2025 example is 2 of 6 (33%) on that reading and 2 of 5 (40%) if a plan's end year is not counted; the constant is one number to move.</t>
+          <t>calcs.comparability takes the union documents and applies the rule (plan_slots, BASE_PLANS=2, BASE_YEARS_SHARE=0.40, VISION_SPAN=10). comparability.csv now carries plans, plan_years, held_in_plans, extracted_in_plans, comparable_in_plans and share_of_plan_years, so the base set can be read at all three grades; why_not states the rule reason and years_why_not the per-year ones. The per-year rule (printed denominator, coverage 0.90 to 1.05) is unchanged underneath. Outcome on 1 September: Thailand is the one comparable country (2017-2021 and 2023-2027, FY2023 to FY2026, 4 of 10 years); Rwanda drops (2017-2024 and 2024-2029 span 13 years, three comparable, 23%). Inclusive counting: the 2020-2025 example is 2 of 6 (33%) on that reading and 2 of 5 (40%) if a plan's end year is not counted; the constant is one number to move.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>The page said eleven Asia-Pacific countries were missing their latest two plans; the interns' upload was complete for all but three, and the gap was on our side in three ways</t>
+          <t>The page said eleven Asia-Pacific countries were missing their latest two plans; the upload was complete for all but three, and the gap was on our side in three ways</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Registered from the bucket into the configs (support/platform/fetch.py --from-bucket, then the ndp and sector lists). plan_period takes the shorter of the periods a front page names, and where the front page prints only bare periods, the one the filename also states. plan_slots and the coverage grid let a long-horizon strategy fill the plan slots where no shorter plan exists, flagged so the page says what it is. Genuinely open after this, on the bucket's own contents: Vietnam (2016-2020 only), Pakistan (no plan in the bucket; the 2024-2029 plan the interns hold has not landed), Maldives (SAP 2019-2023 only). Registering a plan does not extract it: the new plans and sector strategies are screened and on the coverage grid, and stages 1 to 4 have not been run on them.</t>
+          <t>Registered from the bucket into the configs (support/platform/fetch.py --from-bucket, then the ndp and sector lists). plan_period takes the shorter of the periods a front page names, and where the front page prints only bare periods, the one the filename also states. plan_slots and the coverage grid let a long-horizon strategy fill the plan slots where no shorter plan exists, flagged so the page says what it is. Genuinely open after this, on the bucket's own contents: Vietnam (2016-2020 only), Pakistan (no plan in the bucket; the 2024-2029 plan held elsewhere has not landed), Maldives (SAP 2019-2023 only). Registering a plan does not extract it: the new plans and sector strategies are screened and on the coverage grid, and stages 1 to 4 have not been run on them.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Sebastian's decision of 1 September: all 15 comparators from the ALL Comparison (non-APAC) research (Brazil, Colombia, Ghana, Jamaica, Kenya, Rwanda; Egypt, Ethiopia, Jordan, Morocco, Nigeria, Peru, Serbia, Uzbekistan; Kazakhstan) are in scope. Only the six rated good on both sides had been considered and only five built; Colombia, rated good on both, had never been given a config. The research tab itself survives only in the chat record: the workbook copy it was written into (Desktop/Environment_All) is no longer on the machine, and the repo and Downloads copies do not carry the tab.</t>
+          <t>The scope decision of 1 September: all 15 comparators from the ALL Comparison (non-APAC) research (Brazil, Colombia, Ghana, Jamaica, Kenya, Rwanda; Egypt, Ethiopia, Jordan, Morocco, Nigeria, Peru, Serbia, Uzbekistan; Kazakhstan) are in scope. Only the six rated good on both sides had been considered and only five built; Colombia, rated good on both, had never been given a config. The research tab survives only outside this repository: the workbook copy it was written into is no longer available, and the copies that remain do not carry the tab.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>ghana, kenya, maldives, papua_new_guinea, rwanda, samoa, solomon_islands, sri_lanka, timor_leste, tonga</t>
+          <t>cambodia, ghana, kenya, maldives, papua_new_guinea, rwanda, samoa, solomon_islands, sri_lanka, timor_leste, tonga</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>data/calcs/external.csv, columns verdict and scale_flag; python3 -m pv2.validate.external --all</t>
+          <t>data/calcs/external.csv, columns verdict and scale_flag; python3 -m pv2.validate.external --all UPDATE 2026-09-19: Cambodia added. Its three years are held at three scales and its config declares no currency, so nothing converts them: FY2022 prints two grand totals (74,578 and 3,040,826) and the larger is a head; FY2023's grand total, heads and programme rows all equal 61,786, a table that sums to itself, under the unit label 'million baht' because the Khmer was read as Thai script; FY2026 is 4,087.81 against 382,158 of programme rows. FY2023 is 1.96e-09 of the World Bank's figure and passes the scale audit only because its own median is itself. The country is called comparable on that year alone (W141).</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -6967,8 +6967,1015 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>W123</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>mongolia</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Stage 7 stamped every workbook in the sector folder, including the ones the run reused rather than wrote</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Without --force, stage 7 skips a per-document workbook that is already on disk. The run then stamped a glob of the whole folder, so a run that rewrote only the risk grid and the responses put its own time on six Mongolian per-sector workbooks that the 9 September checkout had restored the day before. Beyond STAMP_TOLERANCE_S the audit reads that as a stamp written by a run that did not write the file, so six good workbooks reported stale and the prompt-currency gate could not clear them. Every other stage stamps the paths it wrote; the local helper's parameter is even named paths_written.</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>run.py records the sector folder's mtimes before the two stage 7 writers and stamps only what moved, through provenance.mtimes and provenance.written_since. The six false stamps were removed rather than papered over with a re-extraction, and Mongolia reads current with nothing spent. tests/unit/test_stage7_stamps_what_it_wrote.py pins the helper, the Mongolia shape end to end and the wiring, and fails against the old glob call.</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>provenance.json stamped every sector/*.xlsx at 2026-09-10T07:45:00 while six of the eight carried mtimes of 2026-09-09 10:10:58, a gap of 21.6 hours against a tolerance of one</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>W124</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>A rejected budget year left the mappings built from it on the live path, where they could never be re-made and never stop reading as stale</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Stage 6 and 6b write one workbook per year from that year's budget rows. When the year is later rejected, its budget workbook moves to rejected/ so nothing downstream reads it, but the mappings an earlier run had already written stayed in mappings/. Nothing published was wrong, because the union keys off budget rows and never carried those years. What they did was sit in the currency audit permanently: stage 6 only runs for years that HAVE a budget, so a mapping whose year has none can never be produced again and can never stop being reported as older than the prompt that would now produce it. They were most of what the gate was failing on, and no amount of spending could have cleared a single one.</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>accept.retire_derived moves mappings/&lt;slug&gt;_{mapping,coverage}_&lt;year&gt;.xlsx into rejected/mappings/ when write_rejected retires the year, and the twelve already on disk were retired the same way. tests/unit/test_rejected_year_takes_its_mappings.py pins the move, the years left alone, a second rejection of the same year and a country with no mappings folder.</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>twelve files across six countries on 2026-09-10: fiji 2017, jamaica 2019, kenya 2020 and 2025, kiribati 2023 and 2026, papua_new_guinea 2014, sri_lanka 2022; every orphan year was a rejected year</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>W125</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>India held a budget workbook and a mapping for a fiscal year no source document and no config declares</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>india_budget_2026.xlsx and mappings/india_mapping_2026.xlsx sat in the stage folder with no provenance stamp of any kind, left by a configuration that no longer exists. The config declares 2020 to 2024 and holds no 2026 document, so stage 5 could never rewrite the workbook and the prompt-currency gate could never clear it. No published figure was affected: the union carries India 2021 to 2024 and never 2026. Brazil's three lookalike years are not this fault; they are legitimate from_csv route outputs and are correctly stamped.</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Both files removed. Removing them changed the input hash over the budget glob, so India's remaining mappings correctly re-read as stale and were re-run against the true input set. India also declares 2020 and holds no extraction for it, which is a gap in the backlog rather than a defect.</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>config documents.budget declares 2020-2024; data/llm/india held budget workbooks for 2021, 2022, 2023, 2024 and 2026; provenance.json had no entry for india_budget_2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>W126</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Appendix A of the workflow note published the package test suite as 0 files and 0 lines in every circulated copy</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>The Tests row is labelled workflow/tests/ and globbed support/tests/*.py joined to the workflow directory, which resolves to workflow/support/tests, a path that does not exist. The patterns had lost the ../ that would have reached the entry-point tests, and the row that was meant to count the package's own suite counted nothing. The note gate could not see it: check_note compares the table against what the glob returns, and both were zero.</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>The patterns now read tests/*.py and tests/*/*.py, which is the suite the row names; the entry-point tests keep their own row. Appendix A reads 63 files and 8,357 lines.</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>note_claims.py EXTRAS, Tests row; the published table read 0 and 0 while workflow/tests holds 63 files</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>W127</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>workflow</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>The four model price keys are read by the code and were absent from the credentials example the setup script claims cannot drift from it</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>pv2.extract.config.PRICES reads PRICE_GPT_5_4_MINI_IN, PRICE_GPT_5_4_MINI_OUT, PRICE_GPT_5_4_IN and PRICE_GPT_5_4_OUT with defaults, and they decide every figure the cost ledger, the run reports and the monitoring page state. runbook/01_setup.py generates workflow/.env.example from a hand-maintained list that did not carry them, so the claim that the example cannot drift from the code rested on somebody remembering. A deployment on different rates would have reported the wrong spend with nothing saying so.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>The four keys are in KEYS as optional, with the rates every figure on record was computed at, and a comment names the environment keys that are deliberately not credentials and stay out: the test plumbing and the tuning knobs.</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>28 environment names are read under workflow/pv2; KEYS carried 11 and none of the four price keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>W128</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>The note gate reported a failure to anyone who had just cloned the repository, over a file a clone cannot have</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>The Word copy of the note is generated and data/outputs/ tracks only the panels and run reports, so it does not travel. check_note reported it absent with the same severity as it reported it stale, and a clone therefore met a red gate on arrival over something the reader had not done wrong. A gate that is red on arrival is a gate people learn to ignore. Nothing exercised check_docx at all, so none of its seven assertions had a proof that they fire.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Absent now warns and names the builder; a copy that is present and older than its markdown still fails. test_check_note.py pins both states.</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>a tree built from git ls-files and gated as a stranger would gate it reported FAILED on 'no data/outputs/PV2_Workflow_Documentation.docx'</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>W129</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>nigeria</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>The stage time budget was read from the environment and used by nothing, so a stage that blocked for 35 minutes on a single call passed unremarked</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>config.STAGE_TIME_BUDGET_S has a default of 300 seconds and a comment promising a warning on the report. No code anywhere read it. Nigeria's stage 5 reached section 70 of 79 at 14:05 and was still there at 14:40 with the process at 0% CPU on an established connection to the model endpoint. It was not hung: the last sections of that appropriation truncate at the output cap, so each is retried at max_tokens=64000 and a generation that size takes many minutes. Nothing said so. The client's 300-second timeout is a read timeout and a generation that keeps sending bytes is not a silent socket, so the only thing that would have reported the stage as slow was a constant nobody read, and the run was stopped by hand on a wrong reading of a healthy stage. Restarting cost nothing, because every completed section replayed from cache.</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>llm.Client.map, the one seam every stage's calls pass through, already measured the elapsed time for the ledger and now compares it to the budget and prints a note naming the stage, the elapsed seconds, the item count and the slowest call. It does not stop the stage: a long stage here was correct work, and stopping it would have been the wrong answer. What it buys is that the person watching can tell a slow stage from a stuck one, which is the judgement that was made wrongly without it.</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>grep for STAGE_TIME_BUDGET_S returned its definition in config.py and no reader; nigeria.log last wrote at 14:05:24 with the process holding an ESTABLISHED connection and CPU frozen at 7:45.08 for 35 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>W130</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>workflow</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>A key present and blank in workflow/.env, which is the shape .env.example gives every key, killed the import of pv2.extract.config before any entry point could start</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>runbook/01_setup.py writes .env.example as names with no values and tells a cold machine to copy it to workflow/.env and fill it in. os.environ.get(name, default) returns the empty string for a key that is present and blank, not the default, so a numeric key read that way reached float('') and raised at import time. It had never fired because only credentials were in the example, and a blank credential is a string. The four model price keys joined the example the same day under W127, and with them anybody who copied the example and filled in only the credentials, which is precisely what the setup script instructs, could not run a single entry point. Found by the review of that change and not by any suite: test_setup.py pins that the example carries every key with no value, so the shape the test demands was the shape the import rejected, and the two never met.</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>config._env treats a blank as absent, so the default applies, and a value that is actually set is still read. tests/unit/test_env_example_loads.py loads the whole example as the environment and imports the package, which fails before the change and passes after, plus the two directions of one key.</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_GPT_5_4_MINI_IN= python3 -c 'from pv2.extract import config' raised ValueError: could not convert string to float: '' at config.py:99</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>W131</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>The proof that the note gate can fail had never run: no suite collected it and nothing invoked it, while the register recorded it as run</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>support/platform/test_check_note.py held its nine cases inside a main() with no test function in the file. pytest over support/ collected the file and contributed nothing from it, and no other caller existed: not pv2.validate.suite, not _house.py, not the CI workflow. W91's fix in this register states 'support/platform/test_check_note.py proves the gate fires; pv2.validate.suite runs it', which was not true. A proof nobody executes is the same as no proof, and this file is the whole reason anyone believes the note gate can fail; the note is a circulating document and W126 is an example of it publishing a wrong figure for weeks.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Rewritten as pytest functions, parametrised so a red line names the defect that stopped being caught. The support suite collects fourteen cases from it where it collected none, going from 21 tests to 35. The docx stale case now builds its aged file from arbitrary bytes rather than copying the real one, so it runs on a clone that has never built it. main() still works and now just calls pytest on the file.</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>pytest --collect-only -q support returned 21 tests and none from test_check_note.py; grep for the filename across support, workflow, runbook and _house.py found only its own docstring and this register</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>W132</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>The one-page test fixture was a country in the published tables, and the union tables could not be rebuilt from the stage outputs alone</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>union leaves a country it does not rebuild exactly as it is rather than emptying it, which is the right protection for a country whose stage outputs are not on this machine. The consequence is that a table rebuilt IN PLACE keeps rows a table rebuilt FROM SCRATCH never writes. thailand_test is a one-page plan and a one-page budget the replay suites run against; country.all_slugs() stopped returning it, so no rebuild has written its rows since, and every in-place rebuild has carried them forward. It sat in 22 of the published tables, including comparability.csv, where it read as a country holding one dated plan against a rule that needs two. Nobody could see it from the tree: the baseline suite rebuilds in an isolated tree and so produced 22 MOVED tables against a freeze taken from the live one, which was read as a quirk of the quick mode and recorded as needing a register of permitted differences. It is not a quirk. It is the tables carrying history that the stage outputs do not.</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>data/union and data/calcs were emptied and rebuilt from scratch, which is what a clone does, after checking that thailand_test was the only slug in the tables and not in all_slugs, so nothing real was lost. 46 countries, the fixture gone, and the baseline frozen from that tree now reproduces cell for cell with QUICK_MOVED empty and honestly so. The preservation behaviour itself is unchanged and still right; what is recorded here is that it makes an in-place rebuild and a from-scratch rebuild different, so a freeze is only meaningful when taken from a tree built the way a clone builds it.</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>test_baseline.py --quick reported 22 MOVED tables against a freeze taken from the live tree, every delta matching thailand_test's own row counts (budget_rows -20, risk_summary -11, strategies -5, run_stats -42); after the from-scratch rebuild it reports every output table matching cell for cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>W133</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>all with a sector layer</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 2's presence score measures whether a sector strategy is shaped like a national plan, not how prominent a risk is in it</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 2 scores presence across six key parts of an NDP (title, executive summary, foreword, diagnosis, strategy, monitoring). Stage 1 labels a sector document's paragraphs 'Body Text' and 'Table of Contents / Heading', which map to none of the six, and part 6 is unreachable. So a sector document's likert_presence_score says where its text sits, not what it says: 139 published grid rows score 0 with evidence and direction neutral, 41 score high at 2, and the sector grid's salience spread (low 51%, medium 32%, high 17%) is the inverse of the plan grid's (high 56%, medium 33%, low 11%).</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Migration 0016 drops the one view that exposed the score (v_sector_risk_coverage) and no view, calc or page reads likert any more; render_test refuses a template that does. The score is still written to the grid workbook and the table. Making it mean something on a sector document is a prompt change (a sector-shaped key-part map) and a paid re-run, and is Sebastian's decision.</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Counted 12 September 2026 across sector_risk_grid for the published runs: 139 rows at likert 0 with non-empty risk_evidence and direction neutral; 41 rows salience high at likert 2; salience shares as stated. validate.truth's absence check lists the 139 under 'scored zero and carries evidence'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>W134</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>china, iran, nepal, malaysia, indonesia, and every non-English source</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>The model translates non-English sources and returns the translation in the evidence field, which the page presents as a quotation</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 1 asks for verbatim evidence; prompt 2 relaxes it to 'near-exact' and 'short' with no minimum, and schemas.validate_stage2_object enforces neither. Against a Chinese, Persian, Nepali, Malay or Indonesian paragraph the model writes English prose that matches no paragraph at all: china grid 181 of 204 non-verbatim quotes, iran grid 114 of 117, malaysia 17 of 40 sampled, indonesia 6 of 13. A faithful-looking rendering, not a quotation, and no string check can verify it. Corpus-wide on disk, 29 countries: grid 1,337 of 7,631 quotes (17.5%) are not verbatim and responses 1,056 of 26,238 (4.0%); the grid is worse than the responses everywhere, by 4 to 10 times, because stage 2 is where 'verbatim' became 'near-exact'. In Latin-script countries the remainder are edits: the '; ' join at stages.py:30 glues stage-1 quotes and the model copies the joiner.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>validate.truth classes every quote verbatim, edited, translated or not found by a four-tier match and an English function-word test against the cited paragraph, writes each to the per-country workbook, and the runbook records it as ADVISORY beside every publish; nothing is hidden and nothing is relabelled as evidence. Making the quotes true means re-running stage 2 for every non-English country under a prompt that forbids translation, which is paid and is Sebastian's decision.</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>pv2.validate.truth --all on 13 September 2026, verbatim sheet: the counts above. Ground truth is the paragraphs the model was given (the stage-7 row workbooks), never a fresh PDF parse: pypdf loses 7% of China's text that the model did see.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>W135</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>data/cache is one flat directory of 959,496 files and 4.5 GB, growing about 1 GB a day, with no eviction, no backup, and the only copy of every paid parse</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Every LLM response is cached to data/cache/&lt;sha&gt;.json and every document parse to di_&lt;sha&gt;.json or tl_&lt;sha&gt;.json, in one directory. It held 255,496 files and 1.4 GB on 9 September and 959,496 and 4.5 GB on 12 September. Nothing evicts, it is gitignored and in no backup, and hold.py skipped the parse entries as rebuildable, which they are only by paying Document Intelligence again. Listing the directory takes 27 minutes and a 72 MB listing filled the disk on 12 September.</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>The 566 paid parses were pushed to the outputs bucket under parses/ on 13 September (561 objects, 767 MB); the response entries are worth only what they replay and are not uploaded. Never list the directory: stat the two computed paths for a document. An eviction window for the response entries, and the sweeper that applies it, are Sebastian's decision.</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>os.scandir count and du on 9 and 12 September 2026; the upload log of 13 September; the ENOSPC of 12 September from the listing in the session scratch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>W136</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>123 UNGA General Debate transcripts sat in pv2-sources with no row in source_documents, and 8 of them cannot be registered at all</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Transcripts were uploaded to asia-pacific/&lt;country&gt;/unga/ on 15 September 2026: 31 countries, 2022-2025, named '&lt;Country&gt; - &lt;YYYY&gt; Transcript.pdf'. A query for source_documents rows whose path or storage_path mentions 'unga' returned 0 against 534 rows, and doc_type had no value for them, so nothing in the schema and none of the 43 views could see the corpus. Registering them is 0017 plus support/platform/register_unga.py. Two countries cannot be registered: micronesia and singapore hold 4 transcripts each and have no row in the countries table, and source_documents.country_slug is a foreign key to countries.slug, so the insert is rejected by the database. They are left in the bucket and out of the register on Sebastian's instruction of 15 September, not dropped silently. Separately, nepal's unga/ folder holds only a .emptyFolderPlaceholder, so 32 folders exist and 31 have data; brunei is missing 2024; and fiji's 2023 file is named '(Incomplete)' by whoever uploaded it, so that country-year is partial and is registered as held rather than as a complete statement.</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Registered scope is 29 countries and 115 transcripts. Before any analysis quotes UNGA coverage, read v_unga_coverage rather than counting files in the bucket, since the two differ by the 8 unregistered and the 1 placeholder. To bring micronesia and singapore in, add their countries rows first; that is a decision about whether they are PV2 countries, not a loader fix. Fiji 2023 should be re-fetched complete.</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>pv2-sources listing 15 Sep 2026: 125 objects under */unga/ of which 2 are .emptyFolderPlaceholder; source_documents count where path ilike '%unga%' = 0 of 534; countries table holds 46 slugs, micronesia and singapore absent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>W137</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>112 of the 115 registered UNGA transcripts carry no language, so the register cannot tell a speech delivered in English from a UN translation of one delivered in another language</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>UNGA General Debate addresses are delivered by heads of state, prime ministers and foreign ministers each September in New York. A delegation may speak in any of the six official UN languages or in a national language with interpretation, and what the UN then publishes as the transcript may be the delivered text or an official translation of it. doctype.language_of() reads a language only from an explicit parenthetical in the filename, and 0012 is deliberate that null means nobody has looked, never English. 112 of 115 rows are null on that basis. The corpus therefore does not record, for any country-year, whether the words in the file are the speaker's own or a translator's. That is fine for counting who spoke and when; it is not fine for anything that reads the wording. Any analysis of rhetoric, framing, emphasis or terminology over these files is measuring the translator's word choice wherever the text was translated, and nothing in the register says which rows those are. The three rows that do carry a language are the only ones where the question has been answered at all, and W138 records that even those are ambiguous.</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Before any prompt reads these transcripts for wording rather than for existence, record two things per row: the language of the text in the file, and the language it was delivered in. They are different questions and 0012's single language column answers only the first, so this likely needs a delivery_language column beside it. The UN's own record of the General Debate names the language of delivery per statement and is the source to take it from, not inference from the country. Until then, treat cross-country comparisons of wording as unsupported.</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>source_documents where doc_type='unga', 15 Sep 2026: language null on 112 of 115 rows; the 3 non-null are bn, zh, fr. 0012_source_language.sql: 'null if nobody has looked. Not inferred from country.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>W138</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>bangladesh, china, vanuatu, fiji</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Four UNGA transcripts carry a parenthetical whose meaning is unverified, and each is the only file for its country-year, so a wrong reading loses that year in silence</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Three files are named '(Bengali)', '(Chinese)' and '(French)' and one '(Incomplete)'. Under 0012 a parenthetical marks which EDITION a file is, in a corpus where a country holds an original and a translation of the same document and exactly one is the analysis input. This corpus is not shaped that way: every country-year holds exactly one file. So the parenthetical cannot mean 'the other edition' here, and its actual meaning is unverified. If it marks the language of the text, then Bangladesh 2025, China 2022 and Vanuatu 2024 hold no English text at all and any English-only extraction drops those three country-years while reporting full coverage, because the row is registered and is_analysis_input is true. If instead it marks the language of DELIVERY on a transcript that is itself in English, the three rows are mislabelled and would be wrongly set aside by a language filter. Nobody has opened the files to say which. Fiji 2023 is a separate case of the same shape: '(Incomplete)' is a note from whoever uploaded it, the row is registered as a full analysis input, and how much of the statement is missing is unrecorded.</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Open the four files and record what they actually are. Each is one PDF and the question is answerable in a minute per file. Until then do not quote coverage for bangladesh 2025, china 2022, vanuatu 2024 or fiji 2023 as complete, and do not let a language filter silently include or exclude them. If the three are indeed not in English, the English editions should be fetched from the UN record rather than the year being dropped.</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>pv2-sources 15 Sep 2026: 'Bangladesh - 2025 Transcript (Bengali).pdf', 'China - 2022 Transcript (Chinese).pdf', 'Vanuatu - 2024 Transcript (French).pdf', 'Fiji - 2023 Transcript (Incomplete).pdf'. Each is the sole object for its country-year; all four registered with is_analysis_input true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>W139</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>parser</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>parse.text_layer_is_usable passes a PDF whose text layer decodes to glyph codes rather than words, so an unreadable document reaches a model and is answered with invented content</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>text_layer_coverage counts characters per page and calls a page good at 100 or more. It never asks whether those characters are words. A PDF with a broken or non-standard font encoding yields thousands of characters of punctuation and symbols, so the check returns usable at 100% coverage with the reason 'text layer reaches 6 of 6 pages'. Found on the UNGA POC of 16 September 2026: India 2025 returned 11,950 characters over six pages reading '! " # $ %', pypdf renders the same file as '/0/1/2/1/3/4/1/5', and the stage sent it to the model as a statement. The model produced a fluent, plausible Indian foreign-policy reading: twenty-seven rows with salience, direction and confident quotes, sixteen of which appear nowhere in the file or in any file. Nothing in the pipeline would have caught it, because the only check on evidence is the truth validator's quote matcher and that runs on the sector layer, not here. A corpus-wide scan of the 115 UNGA transcripts found three files in this class: india 2025, china 2024 and china 2025. Five more hold no text layer at all and are correctly refused. The defect is in the shared parser, so it is not confined to UNGA: any document of any type with this encoding is waved through.</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>A legibility test beside the volume test: what share of word-like tokens are common function words. A real statement scores 0.15 to 0.30 in English or French; the three bad files score 0.000 to 0.006. unga_stage8.py now refuses below 0.05 and names the file. The same test belongs in parse.text_layer_is_usable so every stage gets it, which is the change this entry is open for. The three files need Document Intelligence or a re-fetch. India 2025's readings are quarantined out of data/llm/_unga/unga_stage8.json and kept in .with_india2025.bak for inspection. UPDATE 2026-09-16: stage 8 is now wired into pv2.extract.run and reads every statement through Document Intelligence, which works from the rendered page; India 2025 parses to 44 paragraphs and 18 of its 19 quotes are exact. The legibility test is parse.legibility, used by stage 8 before any call; it is not yet inside text_layer_is_usable, which is what keeps this entry open.</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>POC run 16 Sep 2026, 12 statements, $0.31. Verbatim check of 219 quotes claimed non-translated: 192 exact, 5 near, 22 absent, of which 16 are india 2025. text_layer_is_usable('India - 2025 Transcript.pdf') returns (True, 'text layer reaches 6 of 6 pages (100%)'). Run over every text-layer parse the configs name: 2 are not words, both legacy fonts: nepal 'NEP Education Policy 2019.pdf' (84 pages, sector) and maldives budget_2007 (321 pages, budget, the country's parser is text_layer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>W140</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>extraction</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>China's extracted rows mix budgets and count lines twice, so its Extracted and Mapped figures move for reasons that are not the budget</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>The denominator is right: each speech prints the national general public budget (26.7125 trillion yuan in FY2022) and that is what the page divides by. The speech itemises only the central budget (central spending, transfers to local governments, reserves: 12,604.5 billion in FY2022), so coverage sits near half by construction and 'not comparable' is the correct verdict. What is wrong is the numerator. FY2025 carries the other three budget books as heads (government-managed funds 12,488.4, state capital operations 282.3, social insurance funds 11,337.6) and 6,700 of bond and fund programmes under them, all outside the general public budget. FY2024 carries Education twice (1.4 at 164.936 and 1.9 at 164.9) and Science and technology twice (1.5 at 370.828 and 1.13 at 370.8), with sub-items of both beside them, and only four transfer lines (3,173.1) against a transfer head of 10,203.7. The giant transfer line is classed and mapped differently each year, which is why Mapped swings from 12,704 (FY2022) to 5,055 (FY2023).</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>A partition hint in china.json naming the general public budget as the one partition to read (the W102 mechanism), then a stage 5 re-extraction of FY2024 and FY2025 and a stage 6 re-map. Paid: price it with --dry-run first. Not a patch-file entry: excluded_budget_lines needs an exact reconciliation, and none of these rows gives one.</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>data/union/budget_rows.csv, slug china, line_type program and strategy_total; source_location quotes the speech for every head. Found from the dashboard review of 18 September 2026 ('Do these Chinese totals look correct?').</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>W141</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>all; cambodia called comparable on it</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>A year is called comparable when the World Bank contradicts its national total by orders of magnitude, because the per-year rule reads only the document against itself</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>The rule is a printed denominator and coverage of 0.90 to 1.05. A table that sums to itself passes it at exactly 1.00 whatever it is a table of. Cambodia FY2023 does: its 'national total' is 1.96e-09 of the World Bank's figure and the country is comparable on that year alone. The World Bank ratio would catch it, but it cannot be read for the 17 countries whose configs declare no currency, because nothing scales their amounts: Solomon Islands FY2022 and Tonga FY2023 read a ratio of 0.0 for that reason alone, and in millions they sit at 1.15 and 1.32, which is normal. So the test that would catch Cambodia would also, today, demote two good years.</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Declare the 17 missing currencies from each country's books, read by eye (scale.normalise converts nothing without a scale, and converting on a mislabelled file once turned 20.4bn into 2.04e16), re-run union, calcs and the external check, and read every changed year. Then add to the per-year rule: not comparable where the ratio to the World Bank is beyond SCALE_OUTLIER either way. The same declarations are what the USD view on the Regional tab needs. Meanwhile the page takes a comparable country's headline from its comparable years only (Cambodia 112% became 85.5%).</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>data/calcs/shares.csv against data/calcs/external.csv: of 24 comparable years, the World Bank test would demote Cambodia 2023, Nepal 2022, Rwanda 2017, Solomon Islands 2022 and Tonga 2023, and the last two are artefacts of the missing currency. Found from the dashboard review of 18 September 2026 ('how is Cambodia with 112% comparable?').</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K123"/>
+  <autoFilter ref="A1:K142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>